--- a/VRPExample/heuristicapproach/src/furgoni_con_prova.xlsx
+++ b/VRPExample/heuristicapproach/src/furgoni_con_prova.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edoardo\Documents\EPFL\Full-Optimizer\VRPExample\heuristicapproach\src\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\OQI_Project\Full Optimizer\VRPExample\heuristicapproach\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82D54AC-AFDB-4BC7-BD8C-7797548FE198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A8FD66-D4F4-4B6E-8A37-78577B9533CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONSEGNE" sheetId="1" r:id="rId1"/>
@@ -1527,29 +1527,29 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:U164"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.453125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.81640625" style="44" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" style="44" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="24" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.453125" style="45" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.453125" style="45" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="27.453125" style="50" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.42578125" style="45" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.42578125" style="45" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.42578125" style="50" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="23" style="50" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.453125" style="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.453125" style="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.81640625" style="54" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.453125" style="10" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.85546875" style="54" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="18.75" customHeight="1">
@@ -1651,7 +1651,9 @@
       <c r="L2" s="47">
         <v>0.99930555555555556</v>
       </c>
-      <c r="M2" s="35"/>
+      <c r="M2" s="35">
+        <v>30</v>
+      </c>
       <c r="N2" s="34" t="s">
         <v>108</v>
       </c>
@@ -1712,7 +1714,9 @@
       <c r="L3" s="47">
         <v>0.33333333333333331</v>
       </c>
-      <c r="M3" s="35"/>
+      <c r="M3" s="35">
+        <v>30</v>
+      </c>
       <c r="N3" s="20" t="s">
         <v>110</v>
       </c>
@@ -1773,7 +1777,9 @@
       <c r="L4" s="47">
         <v>0.33333333333333331</v>
       </c>
-      <c r="M4" s="35"/>
+      <c r="M4" s="35">
+        <v>30</v>
+      </c>
       <c r="N4" s="34" t="s">
         <v>108</v>
       </c>
@@ -1834,7 +1840,9 @@
       <c r="L5" s="47">
         <v>0.75</v>
       </c>
-      <c r="M5" s="35"/>
+      <c r="M5" s="35">
+        <v>30</v>
+      </c>
       <c r="N5" s="34" t="s">
         <v>110</v>
       </c>
@@ -1895,7 +1903,9 @@
       <c r="L6" s="47">
         <v>0.66666666666666663</v>
       </c>
-      <c r="M6" s="35"/>
+      <c r="M6" s="35">
+        <v>30</v>
+      </c>
       <c r="N6" s="34" t="s">
         <v>108</v>
       </c>
@@ -1956,7 +1966,9 @@
       <c r="L7" s="47">
         <v>0.83333333333333337</v>
       </c>
-      <c r="M7" s="35"/>
+      <c r="M7" s="35">
+        <v>30</v>
+      </c>
       <c r="N7" s="34" t="s">
         <v>110</v>
       </c>
@@ -2017,7 +2029,9 @@
       <c r="L8" s="47">
         <v>0.99930555555555556</v>
       </c>
-      <c r="M8" s="35"/>
+      <c r="M8" s="35">
+        <v>30</v>
+      </c>
       <c r="N8" s="34" t="s">
         <v>108</v>
       </c>
@@ -2078,7 +2092,9 @@
       <c r="L9" s="47">
         <v>0.75</v>
       </c>
-      <c r="M9" s="35"/>
+      <c r="M9" s="35">
+        <v>30</v>
+      </c>
       <c r="N9" s="34" t="s">
         <v>114</v>
       </c>
@@ -2138,7 +2154,9 @@
       <c r="L10" s="47">
         <v>0.70833333333333337</v>
       </c>
-      <c r="M10" s="35"/>
+      <c r="M10" s="35">
+        <v>30</v>
+      </c>
       <c r="N10" s="34" t="s">
         <v>108</v>
       </c>
@@ -2199,7 +2217,9 @@
       <c r="L11" s="47">
         <v>0.75</v>
       </c>
-      <c r="M11" s="35"/>
+      <c r="M11" s="35">
+        <v>30</v>
+      </c>
       <c r="N11" s="34" t="s">
         <v>108</v>
       </c>
@@ -2258,7 +2278,9 @@
       <c r="L12" s="47">
         <v>0.99930555555555556</v>
       </c>
-      <c r="M12" s="35"/>
+      <c r="M12" s="35">
+        <v>30</v>
+      </c>
       <c r="N12" s="34" t="s">
         <v>110</v>
       </c>
@@ -2319,7 +2341,9 @@
       <c r="L13" s="47">
         <v>0.99930555555555556</v>
       </c>
-      <c r="M13" s="35"/>
+      <c r="M13" s="35">
+        <v>30</v>
+      </c>
       <c r="N13" s="34" t="s">
         <v>108</v>
       </c>
@@ -2380,7 +2404,9 @@
       <c r="L14" s="47">
         <v>0.75</v>
       </c>
-      <c r="M14" s="35"/>
+      <c r="M14" s="35">
+        <v>30</v>
+      </c>
       <c r="N14" s="34" t="s">
         <v>108</v>
       </c>
@@ -2439,7 +2465,9 @@
       <c r="L15" s="47">
         <v>0.99930555555555556</v>
       </c>
-      <c r="M15" s="35"/>
+      <c r="M15" s="35">
+        <v>30</v>
+      </c>
       <c r="N15" s="34" t="s">
         <v>110</v>
       </c>
@@ -2500,7 +2528,9 @@
       <c r="L16" s="47">
         <v>0.35416666666666669</v>
       </c>
-      <c r="M16" s="35"/>
+      <c r="M16" s="35">
+        <v>30</v>
+      </c>
       <c r="N16" s="34" t="s">
         <v>108</v>
       </c>
@@ -2561,7 +2591,9 @@
       <c r="L17" s="47">
         <v>0.42708333333333331</v>
       </c>
-      <c r="M17" s="35"/>
+      <c r="M17" s="35">
+        <v>30</v>
+      </c>
       <c r="N17" s="34" t="s">
         <v>110</v>
       </c>
@@ -2621,7 +2653,9 @@
       <c r="L18" s="47">
         <v>0.45833333333333331</v>
       </c>
-      <c r="M18" s="35"/>
+      <c r="M18" s="35">
+        <v>30</v>
+      </c>
       <c r="N18" s="34" t="s">
         <v>108</v>
       </c>
@@ -2681,7 +2715,9 @@
       <c r="L19" s="47">
         <v>0.54166666666666663</v>
       </c>
-      <c r="M19" s="35"/>
+      <c r="M19" s="35">
+        <v>30</v>
+      </c>
       <c r="N19" s="34" t="s">
         <v>110</v>
       </c>
@@ -2741,7 +2777,9 @@
       <c r="L20" s="47">
         <v>0.625</v>
       </c>
-      <c r="M20" s="35"/>
+      <c r="M20" s="35">
+        <v>30</v>
+      </c>
       <c r="N20" s="34" t="s">
         <v>108</v>
       </c>
@@ -2801,7 +2839,9 @@
       <c r="L21" s="47">
         <v>0.35416666666666669</v>
       </c>
-      <c r="M21" s="35"/>
+      <c r="M21" s="35">
+        <v>30</v>
+      </c>
       <c r="N21" s="34" t="s">
         <v>114</v>
       </c>
@@ -2862,7 +2902,9 @@
       <c r="L22" s="47">
         <v>0.75</v>
       </c>
-      <c r="M22" s="35"/>
+      <c r="M22" s="35">
+        <v>30</v>
+      </c>
       <c r="N22" s="34" t="s">
         <v>108</v>
       </c>
@@ -2922,7 +2964,9 @@
       <c r="L23" s="47">
         <v>0.75</v>
       </c>
-      <c r="M23" s="35"/>
+      <c r="M23" s="35">
+        <v>30</v>
+      </c>
       <c r="N23" s="34" t="s">
         <v>110</v>
       </c>
@@ -2982,7 +3026,9 @@
       <c r="L24" s="47">
         <v>0.75</v>
       </c>
-      <c r="M24" s="35"/>
+      <c r="M24" s="35">
+        <v>30</v>
+      </c>
       <c r="N24" s="34" t="s">
         <v>110</v>
       </c>
@@ -3042,7 +3088,9 @@
       <c r="L25" s="47">
         <v>0.75</v>
       </c>
-      <c r="M25" s="35"/>
+      <c r="M25" s="35">
+        <v>30</v>
+      </c>
       <c r="N25" s="34" t="s">
         <v>110</v>
       </c>
@@ -3102,7 +3150,9 @@
       <c r="L26" s="47">
         <v>0.75</v>
       </c>
-      <c r="M26" s="35"/>
+      <c r="M26" s="35">
+        <v>30</v>
+      </c>
       <c r="N26" s="34" t="s">
         <v>110</v>
       </c>
@@ -3162,7 +3212,9 @@
       <c r="L27" s="47">
         <v>0.99930555555555556</v>
       </c>
-      <c r="M27" s="35"/>
+      <c r="M27" s="35">
+        <v>30</v>
+      </c>
       <c r="N27" s="34" t="s">
         <v>108</v>
       </c>
@@ -3222,7 +3274,9 @@
       <c r="L28" s="47">
         <v>0.75</v>
       </c>
-      <c r="M28" s="35"/>
+      <c r="M28" s="35">
+        <v>30</v>
+      </c>
       <c r="N28" s="34" t="s">
         <v>110</v>
       </c>
@@ -3282,7 +3336,9 @@
       <c r="L29" s="48">
         <v>0.99930555555555556</v>
       </c>
-      <c r="M29" s="4"/>
+      <c r="M29" s="35">
+        <v>30</v>
+      </c>
       <c r="N29" s="20" t="s">
         <v>108</v>
       </c>
@@ -3342,7 +3398,9 @@
       <c r="L30" s="48">
         <v>0.39583333333333331</v>
       </c>
-      <c r="M30" s="4"/>
+      <c r="M30" s="35">
+        <v>30</v>
+      </c>
       <c r="N30" s="20" t="s">
         <v>110</v>
       </c>
@@ -3402,7 +3460,9 @@
       <c r="L31" s="48">
         <v>0.99930555555555556</v>
       </c>
-      <c r="M31" s="4"/>
+      <c r="M31" s="35">
+        <v>30</v>
+      </c>
       <c r="N31" s="20" t="s">
         <v>108</v>
       </c>
@@ -3462,7 +3522,9 @@
       <c r="L32" s="48">
         <v>0.35416666666666669</v>
       </c>
-      <c r="M32" s="4"/>
+      <c r="M32" s="35">
+        <v>30</v>
+      </c>
       <c r="N32" s="20" t="s">
         <v>110</v>
       </c>
@@ -3522,7 +3584,9 @@
       <c r="L33" s="47">
         <v>0.66666666666666663</v>
       </c>
-      <c r="M33" s="35"/>
+      <c r="M33" s="35">
+        <v>30</v>
+      </c>
       <c r="N33" s="34" t="s">
         <v>108</v>
       </c>
@@ -3582,7 +3646,9 @@
       <c r="L34" s="47">
         <v>0.35416666666666669</v>
       </c>
-      <c r="M34" s="35"/>
+      <c r="M34" s="35">
+        <v>30</v>
+      </c>
       <c r="N34" s="34" t="s">
         <v>110</v>
       </c>
@@ -3642,7 +3708,9 @@
       <c r="L35" s="47">
         <v>0.75</v>
       </c>
-      <c r="M35" s="35"/>
+      <c r="M35" s="35">
+        <v>30</v>
+      </c>
       <c r="N35" s="34" t="s">
         <v>108</v>
       </c>
@@ -3702,7 +3770,9 @@
       <c r="L36" s="47">
         <v>0.75</v>
       </c>
-      <c r="M36" s="35"/>
+      <c r="M36" s="35">
+        <v>30</v>
+      </c>
       <c r="N36" s="34" t="s">
         <v>110</v>
       </c>
@@ -3725,7 +3795,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="14" customHeight="1">
+    <row r="37" spans="1:20" ht="14.1" customHeight="1">
       <c r="A37" s="35">
         <v>14</v>
       </c>
@@ -3762,7 +3832,9 @@
       <c r="L37" s="47">
         <v>0.75</v>
       </c>
-      <c r="M37" s="35"/>
+      <c r="M37" s="35">
+        <v>30</v>
+      </c>
       <c r="N37" s="34" t="s">
         <v>108</v>
       </c>
@@ -3785,7 +3857,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="14" customHeight="1">
+    <row r="38" spans="1:20" ht="14.1" customHeight="1">
       <c r="A38" s="35">
         <v>14</v>
       </c>
@@ -3822,7 +3894,9 @@
       <c r="L38" s="47">
         <v>0.375</v>
       </c>
-      <c r="M38" s="35"/>
+      <c r="M38" s="35">
+        <v>30</v>
+      </c>
       <c r="N38" s="34" t="s">
         <v>110</v>
       </c>
@@ -3882,7 +3956,9 @@
       <c r="L39" s="47">
         <v>0.375</v>
       </c>
-      <c r="M39" s="35"/>
+      <c r="M39" s="35">
+        <v>30</v>
+      </c>
       <c r="N39" s="34" t="s">
         <v>124</v>
       </c>
@@ -3942,7 +4018,9 @@
       <c r="L40" s="47">
         <v>0.375</v>
       </c>
-      <c r="M40" s="35"/>
+      <c r="M40" s="35">
+        <v>30</v>
+      </c>
       <c r="N40" s="34" t="s">
         <v>114</v>
       </c>
@@ -4002,7 +4080,9 @@
       <c r="L41" s="47">
         <v>0.99930555555555556</v>
       </c>
-      <c r="M41" s="35"/>
+      <c r="M41" s="35">
+        <v>30</v>
+      </c>
       <c r="N41" s="34" t="s">
         <v>124</v>
       </c>
@@ -4062,7 +4142,9 @@
       <c r="L42" s="47">
         <v>0.75</v>
       </c>
-      <c r="M42" s="35"/>
+      <c r="M42" s="35">
+        <v>30</v>
+      </c>
       <c r="N42" s="34" t="s">
         <v>114</v>
       </c>
@@ -4122,7 +4204,9 @@
       <c r="L43" s="48">
         <v>0.99930555555555556</v>
       </c>
-      <c r="M43" s="35"/>
+      <c r="M43" s="35">
+        <v>30</v>
+      </c>
       <c r="N43" s="34" t="s">
         <v>108</v>
       </c>
@@ -4182,7 +4266,9 @@
       <c r="L44" s="47">
         <v>0.75</v>
       </c>
-      <c r="M44" s="35"/>
+      <c r="M44" s="35">
+        <v>30</v>
+      </c>
       <c r="N44" s="34" t="s">
         <v>110</v>
       </c>
@@ -4242,7 +4328,9 @@
       <c r="L45" s="47">
         <v>0.99930555555555556</v>
       </c>
-      <c r="M45" s="35"/>
+      <c r="M45" s="35">
+        <v>30</v>
+      </c>
       <c r="N45" s="34" t="s">
         <v>108</v>
       </c>
@@ -4302,7 +4390,9 @@
       <c r="L46" s="47">
         <v>0.45833333333333331</v>
       </c>
-      <c r="M46" s="35"/>
+      <c r="M46" s="35">
+        <v>30</v>
+      </c>
       <c r="N46" s="34" t="s">
         <v>114</v>
       </c>
@@ -4362,7 +4452,9 @@
       <c r="L47" s="47">
         <v>0.99930555555555556</v>
       </c>
-      <c r="M47" s="35"/>
+      <c r="M47" s="35">
+        <v>30</v>
+      </c>
       <c r="N47" s="34" t="s">
         <v>124</v>
       </c>
@@ -4422,7 +4514,9 @@
       <c r="L48" s="47">
         <v>0.29166666666666669</v>
       </c>
-      <c r="M48" s="35"/>
+      <c r="M48" s="35">
+        <v>30</v>
+      </c>
       <c r="N48" s="34" t="s">
         <v>110</v>
       </c>
@@ -4482,7 +4576,9 @@
       <c r="L49" s="47">
         <v>0.99930555555555556</v>
       </c>
-      <c r="M49" s="35"/>
+      <c r="M49" s="35">
+        <v>30</v>
+      </c>
       <c r="N49" s="34" t="s">
         <v>124</v>
       </c>
@@ -4542,7 +4638,9 @@
       <c r="L50" s="47">
         <v>0.75</v>
       </c>
-      <c r="M50" s="4"/>
+      <c r="M50" s="35">
+        <v>30</v>
+      </c>
       <c r="N50" s="20" t="s">
         <v>114</v>
       </c>
@@ -4602,7 +4700,9 @@
       <c r="L51" s="47">
         <v>0.75</v>
       </c>
-      <c r="M51" s="4"/>
+      <c r="M51" s="35">
+        <v>30</v>
+      </c>
       <c r="N51" s="20" t="s">
         <v>124</v>
       </c>
@@ -4662,7 +4762,9 @@
       <c r="L52" s="47">
         <v>0.75</v>
       </c>
-      <c r="M52" s="4"/>
+      <c r="M52" s="35">
+        <v>30</v>
+      </c>
       <c r="N52" s="20" t="s">
         <v>114</v>
       </c>
@@ -4722,7 +4824,9 @@
       <c r="L53" s="47">
         <v>0.99930555555555556</v>
       </c>
-      <c r="M53" s="35"/>
+      <c r="M53" s="35">
+        <v>30</v>
+      </c>
       <c r="N53" s="34" t="s">
         <v>124</v>
       </c>
@@ -4782,7 +4886,9 @@
       <c r="L54" s="47">
         <v>0.75</v>
       </c>
-      <c r="M54" s="4"/>
+      <c r="M54" s="35">
+        <v>30</v>
+      </c>
       <c r="N54" s="20" t="s">
         <v>114</v>
       </c>
@@ -4842,7 +4948,9 @@
       <c r="L55" s="47">
         <v>0.99930555555555556</v>
       </c>
-      <c r="M55" s="35"/>
+      <c r="M55" s="35">
+        <v>30</v>
+      </c>
       <c r="N55" s="34" t="s">
         <v>124</v>
       </c>
@@ -4902,7 +5010,9 @@
       <c r="L56" s="47">
         <v>0.75</v>
       </c>
-      <c r="M56" s="4"/>
+      <c r="M56" s="35">
+        <v>30</v>
+      </c>
       <c r="N56" s="20" t="s">
         <v>114</v>
       </c>
@@ -4962,7 +5072,9 @@
       <c r="L57" s="47">
         <v>0.99930555555555556</v>
       </c>
-      <c r="M57" s="35"/>
+      <c r="M57" s="35">
+        <v>30</v>
+      </c>
       <c r="N57" s="34" t="s">
         <v>124</v>
       </c>
@@ -5023,7 +5135,9 @@
       <c r="L58" s="47">
         <v>0.75</v>
       </c>
-      <c r="M58" s="4"/>
+      <c r="M58" s="35">
+        <v>30</v>
+      </c>
       <c r="N58" s="20" t="s">
         <v>114</v>
       </c>
@@ -5083,7 +5197,9 @@
       <c r="L59" s="47">
         <v>0.99930555555555556</v>
       </c>
-      <c r="M59" s="35"/>
+      <c r="M59" s="35">
+        <v>30</v>
+      </c>
       <c r="N59" s="34" t="s">
         <v>124</v>
       </c>
@@ -5144,7 +5260,9 @@
       <c r="L60" s="47">
         <v>0.75</v>
       </c>
-      <c r="M60" s="4"/>
+      <c r="M60" s="35">
+        <v>30</v>
+      </c>
       <c r="N60" s="20" t="s">
         <v>114</v>
       </c>
@@ -5204,7 +5322,9 @@
       <c r="L61" s="47">
         <v>0.75</v>
       </c>
-      <c r="M61" s="35"/>
+      <c r="M61" s="35">
+        <v>30</v>
+      </c>
       <c r="N61" s="34" t="s">
         <v>124</v>
       </c>
@@ -5265,7 +5385,9 @@
       <c r="L62" s="47">
         <v>0.75</v>
       </c>
-      <c r="M62" s="4"/>
+      <c r="M62" s="35">
+        <v>30</v>
+      </c>
       <c r="N62" s="20" t="s">
         <v>114</v>
       </c>
@@ -5325,7 +5447,9 @@
       <c r="L63" s="47">
         <v>0.75</v>
       </c>
-      <c r="M63" s="35"/>
+      <c r="M63" s="35">
+        <v>30</v>
+      </c>
       <c r="N63" s="34" t="s">
         <v>124</v>
       </c>
@@ -5386,7 +5510,9 @@
       <c r="L64" s="47">
         <v>0.75</v>
       </c>
-      <c r="M64" s="4"/>
+      <c r="M64" s="35">
+        <v>30</v>
+      </c>
       <c r="N64" s="20" t="s">
         <v>114</v>
       </c>
@@ -5446,7 +5572,9 @@
       <c r="L65" s="47">
         <v>0.99930555555555556</v>
       </c>
-      <c r="M65" s="35"/>
+      <c r="M65" s="35">
+        <v>30</v>
+      </c>
       <c r="N65" s="34" t="s">
         <v>124</v>
       </c>
@@ -5507,7 +5635,9 @@
       <c r="L66" s="47">
         <v>0.75</v>
       </c>
-      <c r="M66" s="4"/>
+      <c r="M66" s="35">
+        <v>30</v>
+      </c>
       <c r="N66" s="20" t="s">
         <v>114</v>
       </c>
@@ -7481,26 +7611,26 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:U38"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.453125" style="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.453125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" style="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.81640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" style="30" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21" style="30" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.453125" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.453125" style="28" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.453125" style="28" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.453125" style="28" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.453125" style="28" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.453125" style="28" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.453125" style="28" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.453125" style="28" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.453125" style="10" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.453125" style="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.453125" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="28" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" style="28" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.7109375" style="28" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="28" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.42578125" style="28" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.42578125" style="28" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="28" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="18.75" customHeight="1">
@@ -9116,11 +9246,11 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D49"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/VRPExample/heuristicapproach/src/furgoni_con_prova.xlsx
+++ b/VRPExample/heuristicapproach/src/furgoni_con_prova.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\OQI_Project\Full Optimizer\VRPExample\heuristicapproach\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A8FD66-D4F4-4B6E-8A37-78577B9533CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D113B9-5BE7-4301-B9A4-F01B975810A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONSEGNE" sheetId="1" r:id="rId1"/>
@@ -2592,7 +2592,7 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="M17" s="35">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N17" s="34" t="s">
         <v>110</v>
@@ -2654,7 +2654,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="M18" s="35">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N18" s="34" t="s">
         <v>108</v>
@@ -2716,7 +2716,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="M19" s="35">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N19" s="34" t="s">
         <v>110</v>
@@ -2778,7 +2778,7 @@
         <v>0.625</v>
       </c>
       <c r="M20" s="35">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N20" s="34" t="s">
         <v>108</v>
@@ -2965,7 +2965,7 @@
         <v>0.75</v>
       </c>
       <c r="M23" s="35">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N23" s="34" t="s">
         <v>110</v>
@@ -3027,7 +3027,7 @@
         <v>0.75</v>
       </c>
       <c r="M24" s="35">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N24" s="34" t="s">
         <v>110</v>
@@ -3089,7 +3089,7 @@
         <v>0.75</v>
       </c>
       <c r="M25" s="35">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N25" s="34" t="s">
         <v>110</v>
@@ -3151,7 +3151,7 @@
         <v>0.75</v>
       </c>
       <c r="M26" s="35">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N26" s="34" t="s">
         <v>110</v>

--- a/VRPExample/heuristicapproach/src/furgoni_con_prova.xlsx
+++ b/VRPExample/heuristicapproach/src/furgoni_con_prova.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\OQI_Project\Full Optimizer\VRPExample\heuristicapproach\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D113B9-5BE7-4301-B9A4-F01B975810A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D79FEDA-36DF-4D8B-B265-C433B1754D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2725,7 +2725,7 @@
         <v>305</v>
       </c>
       <c r="P19" s="52">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Q19" s="35">
         <v>6</v>

--- a/VRPExample/heuristicapproach/src/furgoni_con_prova.xlsx
+++ b/VRPExample/heuristicapproach/src/furgoni_con_prova.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\OQI_Project\Full Optimizer\VRPExample\heuristicapproach\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D79FEDA-36DF-4D8B-B265-C433B1754D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEBC6744-36B9-4F26-A634-38571D66B9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="3765" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONSEGNE" sheetId="1" r:id="rId1"/>
@@ -1530,18 +1530,18 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" customWidth="1"/>
+    <col min="3" max="3" width="36.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" style="10" customWidth="1"/>
     <col min="5" max="5" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" style="44" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="44" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
     <col min="9" max="9" width="27.42578125" style="45" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.42578125" style="45" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="27.42578125" style="50" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23" style="50" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="50" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="50" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="10" customWidth="1"/>
     <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="18.42578125" style="10" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="22.85546875" style="54" bestFit="1" customWidth="1"/>
@@ -1646,7 +1646,7 @@
         <v>126</v>
       </c>
       <c r="K2" s="47">
-        <v>0.33333333333333331</v>
+        <v>0</v>
       </c>
       <c r="L2" s="47">
         <v>0.99930555555555556</v>
@@ -1775,7 +1775,7 @@
         <v>0.25</v>
       </c>
       <c r="L4" s="47">
-        <v>0.33333333333333331</v>
+        <v>0.99930555555555556</v>
       </c>
       <c r="M4" s="35">
         <v>30</v>
@@ -2218,7 +2218,7 @@
         <v>0.75</v>
       </c>
       <c r="M11" s="35">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N11" s="34" t="s">
         <v>108</v>
@@ -2276,7 +2276,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="L12" s="47">
-        <v>0.99930555555555556</v>
+        <v>0.75</v>
       </c>
       <c r="M12" s="35">
         <v>30</v>
@@ -2339,10 +2339,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="L13" s="47">
-        <v>0.99930555555555556</v>
+        <v>0.75</v>
       </c>
       <c r="M13" s="35">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N13" s="34" t="s">
         <v>108</v>
@@ -2463,7 +2463,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="L15" s="47">
-        <v>0.99930555555555556</v>
+        <v>0.75</v>
       </c>
       <c r="M15" s="35">
         <v>30</v>
@@ -2472,7 +2472,7 @@
         <v>110</v>
       </c>
       <c r="O15" s="35">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P15" s="52">
         <v>1.5</v>
@@ -2837,7 +2837,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="L21" s="47">
-        <v>0.35416666666666669</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="M21" s="35">
         <v>30</v>
@@ -2897,7 +2897,7 @@
         <v>126</v>
       </c>
       <c r="K22" s="47">
-        <v>0.33333333333333331</v>
+        <v>0.20833333333333334</v>
       </c>
       <c r="L22" s="47">
         <v>0.75</v>
@@ -3331,7 +3331,7 @@
         <v>126</v>
       </c>
       <c r="K29" s="48">
-        <v>0.33333333333333331</v>
+        <v>0</v>
       </c>
       <c r="L29" s="48">
         <v>0.99930555555555556</v>
@@ -3827,7 +3827,7 @@
         <v>126</v>
       </c>
       <c r="K37" s="47">
-        <v>0.25</v>
+        <v>0.20833333333333334</v>
       </c>
       <c r="L37" s="47">
         <v>0.75</v>
@@ -4447,7 +4447,7 @@
         <v>126</v>
       </c>
       <c r="K47" s="47">
-        <v>0.33333333333333331</v>
+        <v>0</v>
       </c>
       <c r="L47" s="47">
         <v>0.99930555555555556</v>
